--- a/data/trans_orig/P36B06_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P36B06_R-Provincia-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que consume fruta fresca (excluyendo zumos) al menos 3 veces por semana en 2007</t>
+          <t>Población que consume fruta fresca (excluyendo zumos) al menos 3 veces por semana en 2007 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>180337</t>
+          <t>179935</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>210739</t>
+          <t>209375</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>66,06%</t>
+          <t>65,91%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>77,19%</t>
+          <t>76,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>195808</t>
+          <t>193678</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>222831</t>
+          <t>220857</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>75,07%</t>
+          <t>74,25%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>85,43%</t>
+          <t>84,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>384400</t>
+          <t>384377</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>424665</t>
+          <t>424971</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>72,01%</t>
+          <t>72,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>79,55%</t>
+          <t>79,61%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>62271</t>
+          <t>63635</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>92673</t>
+          <t>93075</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>33,94%</t>
+          <t>34,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>38007</t>
+          <t>39981</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>65030</t>
+          <t>67160</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>109183</t>
+          <t>108877</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>149448</t>
+          <t>149471</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>28,0%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>329623</t>
+          <t>329089</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>370712</t>
+          <t>371771</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>67,12%</t>
+          <t>67,01%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>75,49%</t>
+          <t>75,7%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>348952</t>
+          <t>349346</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>389055</t>
+          <t>390436</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>69,24%</t>
+          <t>69,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>77,2%</t>
+          <t>77,48%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>691395</t>
+          <t>691599</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>747898</t>
+          <t>747257</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>69,48%</t>
+          <t>69,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>75,16%</t>
+          <t>75,1%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>120373</t>
+          <t>119314</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>161462</t>
+          <t>161996</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>32,99%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>114894</t>
+          <t>113513</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>154997</t>
+          <t>154603</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>30,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>247136</t>
+          <t>247777</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>303639</t>
+          <t>303435</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>30,49%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>241277</t>
+          <t>240570</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>271006</t>
+          <t>269738</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>75,67%</t>
+          <t>75,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>85,0%</t>
+          <t>84,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>289063</t>
+          <t>289989</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>310956</t>
+          <t>311415</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>86,18%</t>
+          <t>86,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>539308</t>
+          <t>538658</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>576175</t>
+          <t>573234</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>82,43%</t>
+          <t>82,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>88,07%</t>
+          <t>87,62%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>47840</t>
+          <t>49108</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>77569</t>
+          <t>78276</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>24456</t>
+          <t>23997</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>46349</t>
+          <t>45423</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>78083</t>
+          <t>81024</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>114950</t>
+          <t>115600</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,67%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>284726</t>
+          <t>284910</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>311985</t>
+          <t>313562</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>79,38%</t>
+          <t>79,43%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>86,98%</t>
+          <t>87,42%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>321361</t>
+          <t>323149</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>344161</t>
+          <t>344372</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>86,51%</t>
+          <t>87,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>615711</t>
+          <t>614381</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>651436</t>
+          <t>649957</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>84,33%</t>
+          <t>84,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>89,22%</t>
+          <t>89,02%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>46686</t>
+          <t>45109</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>73945</t>
+          <t>73761</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>27295</t>
+          <t>27084</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>50095</t>
+          <t>48307</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>78691</t>
+          <t>80170</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>114416</t>
+          <t>115746</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,85%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>119752</t>
+          <t>120064</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>146849</t>
+          <t>146343</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>58,9%</t>
+          <t>59,06%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>72,23%</t>
+          <t>71,98%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>132766</t>
+          <t>132989</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>160021</t>
+          <t>159803</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>63,93%</t>
+          <t>64,04%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>77,06%</t>
+          <t>76,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>260317</t>
+          <t>261073</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>298217</t>
+          <t>299728</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>63,34%</t>
+          <t>63,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>72,56%</t>
+          <t>72,93%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>56459</t>
+          <t>56965</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>83556</t>
+          <t>83244</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>41,1%</t>
+          <t>40,94%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>47647</t>
+          <t>47865</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>74902</t>
+          <t>74679</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>36,07%</t>
+          <t>35,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>112759</t>
+          <t>111248</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>150659</t>
+          <t>149903</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>27,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>36,66%</t>
+          <t>36,47%</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>208435</t>
+          <t>208001</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>233906</t>
+          <t>233848</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>76,97%</t>
+          <t>76,81%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>86,37%</t>
+          <t>86,35%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>220501</t>
+          <t>219491</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>244032</t>
+          <t>243608</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>79,28%</t>
+          <t>78,91%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>87,58%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>437166</t>
+          <t>436200</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>470576</t>
+          <t>470742</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>79,64%</t>
+          <t>79,46%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>85,72%</t>
+          <t>85,75%</t>
         </is>
       </c>
     </row>
@@ -2560,12 +2560,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>36905</t>
+          <t>36963</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>62376</t>
+          <t>62810</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2575,12 +2575,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>34112</t>
+          <t>34536</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>57643</t>
+          <t>58653</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>78379</t>
+          <t>78213</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>111789</t>
+          <t>112755</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,54%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>480781</t>
+          <t>479827</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>519879</t>
+          <t>519554</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>78,17%</t>
+          <t>78,02%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>84,53%</t>
+          <t>84,48%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>526963</t>
+          <t>527551</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>562446</t>
+          <t>561693</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>82,69%</t>
+          <t>82,79%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>88,26%</t>
+          <t>88,14%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1020314</t>
+          <t>1020631</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1074270</t>
+          <t>1071446</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>81,48%</t>
+          <t>81,5%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>85,79%</t>
+          <t>85,56%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>95148</t>
+          <t>95473</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>134246</t>
+          <t>135200</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>74797</t>
+          <t>75550</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>110280</t>
+          <t>109692</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>178000</t>
+          <t>180824</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>231956</t>
+          <t>231639</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>18,5%</t>
         </is>
       </c>
     </row>
@@ -3133,12 +3133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>509970</t>
+          <t>510364</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>558427</t>
+          <t>558071</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3148,12 +3148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>68,64%</t>
+          <t>68,7%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>75,17%</t>
+          <t>75,12%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>593568</t>
+          <t>592483</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>638630</t>
+          <t>641107</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3183,12 +3183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>75,86%</t>
+          <t>75,72%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>81,62%</t>
+          <t>81,94%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1115166</t>
+          <t>1117657</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1184919</t>
+          <t>1188717</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>73,11%</t>
+          <t>73,27%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>77,68%</t>
+          <t>77,93%</t>
         </is>
       </c>
     </row>
@@ -3246,12 +3246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>184486</t>
+          <t>184842</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>232943</t>
+          <t>232549</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3261,12 +3261,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>31,36%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>143821</t>
+          <t>141344</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>188883</t>
+          <t>189968</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3296,12 +3296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>340445</t>
+          <t>336647</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>410198</t>
+          <t>407707</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3331,12 +3331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>26,73%</t>
         </is>
       </c>
     </row>
@@ -3476,12 +3476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2449382</t>
+          <t>2451498</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2544630</t>
+          <t>2550722</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3491,12 +3491,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>74,82%</t>
+          <t>74,89%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>77,73%</t>
+          <t>77,92%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2709677</t>
+          <t>2713392</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2799375</t>
+          <t>2798214</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3526,12 +3526,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>80,24%</t>
+          <t>80,35%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>82,89%</t>
+          <t>82,86%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>5177785</t>
+          <t>5185270</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5322608</t>
+          <t>5322071</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3561,12 +3561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>77,85%</t>
+          <t>77,96%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>80,03%</t>
+          <t>80,02%</t>
         </is>
       </c>
     </row>
@@ -3589,12 +3589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>729041</t>
+          <t>722949</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>824289</t>
+          <t>822173</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>25,11%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>577787</t>
+          <t>578948</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>667485</t>
+          <t>663770</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3639,12 +3639,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1328225</t>
+          <t>1328762</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1473048</t>
+          <t>1465563</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3674,12 +3674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>22,04%</t>
         </is>
       </c>
     </row>
@@ -3860,7 +3860,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que consume fruta fresca (excluyendo zumos) al menos 3 veces por semana en 2012</t>
+          <t>Población que consume fruta fresca (excluyendo zumos) al menos 3 veces por semana en 2012 (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>204298</t>
+          <t>205169</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>234385</t>
+          <t>235257</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>69,32%</t>
+          <t>69,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>79,52%</t>
+          <t>79,82%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>204598</t>
+          <t>205206</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>234238</t>
+          <t>234980</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>71,79%</t>
+          <t>72,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>82,19%</t>
+          <t>82,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>419145</t>
+          <t>418631</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>461486</t>
+          <t>461671</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>72,3%</t>
+          <t>72,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>79,6%</t>
+          <t>79,63%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>60353</t>
+          <t>59481</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>90440</t>
+          <t>89569</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,68%</t>
+          <t>30,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>50768</t>
+          <t>50026</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>80408</t>
+          <t>79800</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>28,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>118258</t>
+          <t>118073</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>160599</t>
+          <t>161113</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>27,79%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>412250</t>
+          <t>412290</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>445532</t>
+          <t>445741</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4418,7 +4418,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>88,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>443233</t>
+          <t>443440</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>473313</t>
+          <t>475182</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>84,62%</t>
+          <t>84,66%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>90,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>865661</t>
+          <t>868480</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>910904</t>
+          <t>911773</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>84,19%</t>
+          <t>84,46%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>88,59%</t>
+          <t>88,67%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>58955</t>
+          <t>58746</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>92237</t>
+          <t>92197</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4526,7 +4526,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>50452</t>
+          <t>48583</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>80532</t>
+          <t>80325</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>117348</t>
+          <t>116479</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>162591</t>
+          <t>159772</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,54%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>272612</t>
+          <t>273402</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>295192</t>
+          <t>295564</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>84,13%</t>
+          <t>84,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>91,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>305234</t>
+          <t>304802</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>324905</t>
+          <t>325266</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>89,77%</t>
+          <t>89,64%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>585546</t>
+          <t>583992</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>615780</t>
+          <t>615712</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>87,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,72%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>28854</t>
+          <t>28482</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>51434</t>
+          <t>50644</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>15129</t>
+          <t>14768</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>34800</t>
+          <t>35232</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>48300</t>
+          <t>48368</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>78534</t>
+          <t>80088</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>12,06%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>291210</t>
+          <t>291436</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>323140</t>
+          <t>321666</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>77,87%</t>
+          <t>77,93%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>86,41%</t>
+          <t>86,01%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>350343</t>
+          <t>349533</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>370460</t>
+          <t>370253</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>89,87%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>648733</t>
+          <t>647118</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>685941</t>
+          <t>685244</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>85,03%</t>
+          <t>84,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>89,91%</t>
+          <t>89,82%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>50842</t>
+          <t>52316</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>82772</t>
+          <t>82546</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>18491</t>
+          <t>18698</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>38608</t>
+          <t>39418</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>76992</t>
+          <t>77689</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>114200</t>
+          <t>115815</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>15,18%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>144171</t>
+          <t>142629</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>171469</t>
+          <t>170629</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>67,81%</t>
+          <t>67,08%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>80,65%</t>
+          <t>80,25%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>180426</t>
+          <t>179947</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>200276</t>
+          <t>199819</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>82,16%</t>
+          <t>81,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>91,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>330402</t>
+          <t>331061</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>364995</t>
+          <t>364397</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>76,44%</t>
+          <t>76,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>84,45%</t>
+          <t>84,31%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>41149</t>
+          <t>41989</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>68447</t>
+          <t>69989</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>32,19%</t>
+          <t>32,92%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>19315</t>
+          <t>19772</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>39165</t>
+          <t>39644</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>67214</t>
+          <t>67812</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>101807</t>
+          <t>101148</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,4%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>232543</t>
+          <t>232466</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>252829</t>
+          <t>252338</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>85,17%</t>
+          <t>85,15%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,42%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>235419</t>
+          <t>236628</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>259026</t>
+          <t>257961</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>84,4%</t>
+          <t>84,83%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>475730</t>
+          <t>475743</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>507204</t>
+          <t>505939</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5860,7 +5860,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>91,66%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>20193</t>
+          <t>20684</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>40479</t>
+          <t>40556</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>19918</t>
+          <t>20983</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>43525</t>
+          <t>42316</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>44762</t>
+          <t>46027</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>76236</t>
+          <t>76223</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5968,7 +5968,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>542343</t>
+          <t>541420</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>578573</t>
+          <t>579045</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>82,21%</t>
+          <t>82,07%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>87,77%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>586939</t>
+          <t>585253</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>622967</t>
+          <t>622720</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>84,96%</t>
+          <t>84,72%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>90,18%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1140293</t>
+          <t>1143134</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1194322</t>
+          <t>1192712</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>84,43%</t>
+          <t>84,64%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>88,43%</t>
+          <t>88,31%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>81152</t>
+          <t>80680</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>117382</t>
+          <t>118305</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>67861</t>
+          <t>68108</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>103889</t>
+          <t>105575</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>156231</t>
+          <t>157841</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>210260</t>
+          <t>207419</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,36%</t>
         </is>
       </c>
     </row>
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>624993</t>
+          <t>625819</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>667123</t>
+          <t>667888</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>80,22%</t>
+          <t>80,33%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>85,63%</t>
+          <t>85,73%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>690319</t>
+          <t>689342</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>731879</t>
+          <t>731596</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>83,79%</t>
+          <t>83,67%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>88,84%</t>
+          <t>88,8%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6526,12 +6526,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1328415</t>
+          <t>1327345</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1387272</t>
+          <t>1385826</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6541,12 +6541,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>82,87%</t>
+          <t>82,81%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>86,54%</t>
+          <t>86,45%</t>
         </is>
       </c>
     </row>
@@ -6569,12 +6569,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>111975</t>
+          <t>111210</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>154105</t>
+          <t>153279</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>91974</t>
+          <t>92257</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>133534</t>
+          <t>134511</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>215679</t>
+          <t>217125</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>274536</t>
+          <t>275606</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6654,12 +6654,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>17,19%</t>
         </is>
       </c>
     </row>
@@ -6799,12 +6799,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2812667</t>
+          <t>2801621</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2899943</t>
+          <t>2893006</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>82,2%</t>
+          <t>81,88%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>84,75%</t>
+          <t>84,55%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3078892</t>
+          <t>3070752</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3154466</t>
+          <t>3152914</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>86,71%</t>
+          <t>86,48%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>88,79%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6869,12 +6869,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>5912374</t>
+          <t>5907117</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>6029929</t>
+          <t>6026951</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6884,12 +6884,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>84,79%</t>
+          <t>84,72%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>86,44%</t>
         </is>
       </c>
     </row>
@@ -6912,12 +6912,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>521774</t>
+          <t>528711</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>609050</t>
+          <t>620096</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>396506</t>
+          <t>398058</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>472080</t>
+          <t>480220</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>942760</t>
+          <t>945738</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1060315</t>
+          <t>1065572</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6997,12 +6997,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,28%</t>
         </is>
       </c>
     </row>
@@ -7183,7 +7183,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que consume fruta fresca (excluyendo zumos) al menos 3 veces por semana en 2016</t>
+          <t>Población que consume fruta fresca (excluyendo zumos) al menos 3 veces por semana en 2016 (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7378,12 +7378,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>205640</t>
+          <t>207074</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>236113</t>
+          <t>236237</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7393,12 +7393,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>70,49%</t>
+          <t>70,98%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>80,94%</t>
+          <t>80,98%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>219251</t>
+          <t>219286</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>245844</t>
+          <t>246345</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7428,12 +7428,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>75,94%</t>
+          <t>75,96%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>85,15%</t>
+          <t>85,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7448,12 +7448,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>432837</t>
+          <t>435131</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>474422</t>
+          <t>475753</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7463,12 +7463,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>74,57%</t>
+          <t>74,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>81,74%</t>
+          <t>81,97%</t>
         </is>
       </c>
     </row>
@@ -7491,12 +7491,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>55615</t>
+          <t>55491</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>86088</t>
+          <t>84654</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7506,12 +7506,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>29,02%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>42859</t>
+          <t>42358</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>69452</t>
+          <t>69417</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7541,12 +7541,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7561,12 +7561,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>106009</t>
+          <t>104678</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>147594</t>
+          <t>145300</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7576,12 +7576,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>25,03%</t>
         </is>
       </c>
     </row>
@@ -7721,12 +7721,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>413467</t>
+          <t>414254</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>445231</t>
+          <t>445803</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7736,12 +7736,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>82,27%</t>
+          <t>82,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>88,59%</t>
+          <t>88,7%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>464732</t>
+          <t>465373</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>490823</t>
+          <t>490279</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7771,12 +7771,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>88,84%</t>
+          <t>88,97%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7791,12 +7791,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>888324</t>
+          <t>884847</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>928927</t>
+          <t>927569</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7806,12 +7806,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>86,61%</t>
+          <t>86,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>90,44%</t>
         </is>
       </c>
     </row>
@@ -7834,12 +7834,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>57344</t>
+          <t>56772</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>89108</t>
+          <t>88321</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7849,12 +7849,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>32261</t>
+          <t>32805</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>58352</t>
+          <t>57711</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7884,12 +7884,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7904,12 +7904,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>96732</t>
+          <t>98090</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>137335</t>
+          <t>140812</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7919,12 +7919,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,73%</t>
         </is>
       </c>
     </row>
@@ -8064,12 +8064,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>252608</t>
+          <t>252897</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>278017</t>
+          <t>278921</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8079,12 +8079,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>79,3%</t>
+          <t>79,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>87,27%</t>
+          <t>87,56%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>278949</t>
+          <t>277258</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>302781</t>
+          <t>302348</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8114,12 +8114,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>82,94%</t>
+          <t>82,44%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>89,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8134,12 +8134,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>541418</t>
+          <t>538413</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>576792</t>
+          <t>575078</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8149,12 +8149,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>82,68%</t>
+          <t>82,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>87,82%</t>
         </is>
       </c>
     </row>
@@ -8177,12 +8177,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>40548</t>
+          <t>39644</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>65957</t>
+          <t>65668</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8192,12 +8192,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>33528</t>
+          <t>33961</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>57360</t>
+          <t>59051</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8227,12 +8227,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8247,12 +8247,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>78082</t>
+          <t>79796</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>113456</t>
+          <t>116461</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8262,12 +8262,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,78%</t>
         </is>
       </c>
     </row>
@@ -8407,12 +8407,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>280115</t>
+          <t>280302</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>309792</t>
+          <t>310991</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8422,12 +8422,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>75,71%</t>
+          <t>75,76%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>83,74%</t>
+          <t>84,06%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8442,12 +8442,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>318129</t>
+          <t>316517</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>345234</t>
+          <t>345591</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8457,12 +8457,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>82,14%</t>
+          <t>81,73%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>89,14%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8477,12 +8477,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>605648</t>
+          <t>607221</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>648490</t>
+          <t>649629</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8492,12 +8492,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>79,98%</t>
+          <t>80,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>85,64%</t>
+          <t>85,79%</t>
         </is>
       </c>
     </row>
@@ -8520,12 +8520,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>60172</t>
+          <t>58973</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>89849</t>
+          <t>89662</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8535,12 +8535,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8555,12 +8555,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>42049</t>
+          <t>41692</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>69154</t>
+          <t>70766</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8570,12 +8570,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>108757</t>
+          <t>107618</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>151599</t>
+          <t>150026</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8605,12 +8605,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>19,81%</t>
         </is>
       </c>
     </row>
@@ -8750,12 +8750,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>182995</t>
+          <t>182397</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>200207</t>
+          <t>199804</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8765,12 +8765,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>86,64%</t>
+          <t>86,35%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8785,12 +8785,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>196498</t>
+          <t>197872</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>211279</t>
+          <t>211449</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8800,47 +8800,47 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
+          <t>90,52%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>96,73%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>404</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>398559</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>386374</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>408689</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>92,73%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
           <t>89,89%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>96,66%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>404</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>398559</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>385860</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>407797</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>92,73%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>89,77%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>95,09%</t>
         </is>
       </c>
     </row>
@@ -8863,12 +8863,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11014</t>
+          <t>11417</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>28226</t>
+          <t>28824</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8878,12 +8878,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8898,12 +8898,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7308</t>
+          <t>7138</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>22089</t>
+          <t>20715</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8913,47 +8913,47 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
+          <t>9,48%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>31249</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>21119</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>43434</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>7,27%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>4,91%</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
           <t>10,11%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>31249</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>22011</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>43948</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>7,27%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>5,12%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>10,23%</t>
         </is>
       </c>
     </row>
@@ -9093,12 +9093,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>145478</t>
+          <t>146049</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>177107</t>
+          <t>178656</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>55,29%</t>
+          <t>55,51%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>67,31%</t>
+          <t>67,9%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9128,12 +9128,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>161976</t>
+          <t>159833</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>193909</t>
+          <t>193494</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9143,12 +9143,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>59,53%</t>
+          <t>58,74%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>71,26%</t>
+          <t>71,11%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>315908</t>
+          <t>315333</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>361999</t>
+          <t>361406</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9178,12 +9178,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>59,02%</t>
+          <t>58,92%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>67,63%</t>
+          <t>67,52%</t>
         </is>
       </c>
     </row>
@@ -9206,12 +9206,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>86016</t>
+          <t>84467</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>117645</t>
+          <t>117074</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>32,1%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>44,71%</t>
+          <t>44,49%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9241,12 +9241,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>78194</t>
+          <t>78609</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>110127</t>
+          <t>112270</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9256,12 +9256,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>28,74%</t>
+          <t>28,89%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>40,47%</t>
+          <t>41,26%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9276,12 +9276,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>173227</t>
+          <t>173820</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>219318</t>
+          <t>219893</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9291,12 +9291,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>40,98%</t>
+          <t>41,08%</t>
         </is>
       </c>
     </row>
@@ -9436,12 +9436,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>447568</t>
+          <t>445934</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>497236</t>
+          <t>494493</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9451,12 +9451,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>68,56%</t>
+          <t>68,31%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>76,17%</t>
+          <t>75,75%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9471,12 +9471,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>494914</t>
+          <t>496867</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>543151</t>
+          <t>544324</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9486,12 +9486,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>71,71%</t>
+          <t>71,99%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>78,7%</t>
+          <t>78,87%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9506,12 +9506,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>958164</t>
+          <t>955082</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1023803</t>
+          <t>1023547</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9521,12 +9521,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>71,35%</t>
+          <t>71,12%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>76,23%</t>
+          <t>76,22%</t>
         </is>
       </c>
     </row>
@@ -9549,12 +9549,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>155542</t>
+          <t>158285</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>205210</t>
+          <t>206844</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9584,12 +9584,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>147031</t>
+          <t>145858</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>195268</t>
+          <t>193315</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9599,12 +9599,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9619,12 +9619,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>319156</t>
+          <t>319412</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>384795</t>
+          <t>387877</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9634,12 +9634,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>28,88%</t>
         </is>
       </c>
     </row>
@@ -9779,12 +9779,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>651885</t>
+          <t>650847</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>688555</t>
+          <t>691149</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9794,12 +9794,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>83,83%</t>
+          <t>83,7%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>88,55%</t>
+          <t>88,88%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9814,12 +9814,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>686583</t>
+          <t>687708</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>727549</t>
+          <t>729299</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9829,12 +9829,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>83,48%</t>
+          <t>83,62%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>88,67%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9849,12 +9849,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1351440</t>
+          <t>1352658</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1407097</t>
+          <t>1406901</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9864,12 +9864,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>84,46%</t>
+          <t>84,54%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>87,94%</t>
+          <t>87,93%</t>
         </is>
       </c>
     </row>
@@ -9892,12 +9892,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>89041</t>
+          <t>86447</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>125711</t>
+          <t>126749</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9907,12 +9907,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9927,12 +9927,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>94913</t>
+          <t>93163</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>135879</t>
+          <t>134754</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9942,12 +9942,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9962,12 +9962,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>192961</t>
+          <t>193157</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>248618</t>
+          <t>247400</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9977,12 +9977,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,46%</t>
         </is>
       </c>
     </row>
@@ -10122,12 +10122,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2660576</t>
+          <t>2663191</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2752130</t>
+          <t>2759808</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10137,12 +10137,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>78,54%</t>
+          <t>78,62%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>81,24%</t>
+          <t>81,47%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10157,12 +10157,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2905980</t>
+          <t>2906414</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2993329</t>
+          <t>2999309</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10172,12 +10172,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>82,13%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>84,59%</t>
+          <t>84,76%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10192,12 +10192,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>5590496</t>
+          <t>5597182</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5724540</t>
+          <t>5726172</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10207,12 +10207,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>80,71%</t>
+          <t>80,81%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>82,65%</t>
+          <t>82,67%</t>
         </is>
       </c>
     </row>
@@ -10235,12 +10235,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>635420</t>
+          <t>627742</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>726974</t>
+          <t>724359</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10250,12 +10250,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10270,12 +10270,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>545383</t>
+          <t>539403</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>632732</t>
+          <t>632298</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10285,12 +10285,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10305,12 +10305,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1201723</t>
+          <t>1200091</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1335767</t>
+          <t>1329081</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10320,12 +10320,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,19%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P36B06_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P36B06_R-Provincia-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>179935</t>
+          <t>179529</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>209375</t>
+          <t>209356</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>65,91%</t>
+          <t>65,76%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>76,69%</t>
+          <t>76,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>193678</t>
+          <t>195279</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>220857</t>
+          <t>220592</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>74,25%</t>
+          <t>74,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>84,67%</t>
+          <t>84,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>384377</t>
+          <t>385053</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>424971</t>
+          <t>426065</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>72,0%</t>
+          <t>72,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>79,61%</t>
+          <t>79,81%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>63635</t>
+          <t>63654</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>93075</t>
+          <t>93481</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34,09%</t>
+          <t>34,24%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>39981</t>
+          <t>40246</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>67160</t>
+          <t>65559</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>108877</t>
+          <t>107783</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>149471</t>
+          <t>148795</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>27,87%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>329089</t>
+          <t>331164</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>371771</t>
+          <t>370038</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>67,01%</t>
+          <t>67,44%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>75,7%</t>
+          <t>75,35%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>349346</t>
+          <t>349336</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>390436</t>
+          <t>387540</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>77,48%</t>
+          <t>76,9%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>691599</t>
+          <t>690794</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>747257</t>
+          <t>747394</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>69,51%</t>
+          <t>69,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>75,1%</t>
+          <t>75,11%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>119314</t>
+          <t>121047</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>161996</t>
+          <t>159921</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>32,99%</t>
+          <t>32,56%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>113513</t>
+          <t>116409</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>154603</t>
+          <t>154613</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>247777</t>
+          <t>247640</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>303435</t>
+          <t>304240</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>30,58%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>240570</t>
+          <t>242204</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>269738</t>
+          <t>270319</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>75,45%</t>
+          <t>75,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>84,6%</t>
+          <t>84,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>289989</t>
+          <t>288046</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>311415</t>
+          <t>310132</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>86,46%</t>
+          <t>85,88%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>538658</t>
+          <t>536441</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>573234</t>
+          <t>574333</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>82,33%</t>
+          <t>81,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>87,62%</t>
+          <t>87,78%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>49108</t>
+          <t>48527</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>78276</t>
+          <t>76642</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>23997</t>
+          <t>25280</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>45423</t>
+          <t>47366</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>81024</t>
+          <t>79925</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>115600</t>
+          <t>117817</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>18,01%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>284910</t>
+          <t>282774</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>313562</t>
+          <t>312418</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>79,43%</t>
+          <t>78,84%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>87,42%</t>
+          <t>87,1%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>323149</t>
+          <t>322167</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>344372</t>
+          <t>344331</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>87,0%</t>
+          <t>86,73%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>92,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>614381</t>
+          <t>616045</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>649957</t>
+          <t>650276</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>84,15%</t>
+          <t>84,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>89,06%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>45109</t>
+          <t>46253</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>73761</t>
+          <t>75897</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>27084</t>
+          <t>27125</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>48307</t>
+          <t>49289</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>80170</t>
+          <t>79851</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>115746</t>
+          <t>114082</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>15,62%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>120064</t>
+          <t>119430</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>146343</t>
+          <t>145486</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>59,06%</t>
+          <t>58,74%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>71,98%</t>
+          <t>71,56%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>132989</t>
+          <t>132520</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>159803</t>
+          <t>159033</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>64,04%</t>
+          <t>63,81%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>76,95%</t>
+          <t>76,58%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>261073</t>
+          <t>261813</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>299728</t>
+          <t>298534</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>63,53%</t>
+          <t>63,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>72,93%</t>
+          <t>72,64%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>56965</t>
+          <t>57822</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>83244</t>
+          <t>83878</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>28,44%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>40,94%</t>
+          <t>41,26%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>47865</t>
+          <t>48635</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>74679</t>
+          <t>75148</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>35,96%</t>
+          <t>36,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>111248</t>
+          <t>112442</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>149903</t>
+          <t>149163</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>36,47%</t>
+          <t>36,29%</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>208001</t>
+          <t>207837</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>233848</t>
+          <t>233959</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>76,81%</t>
+          <t>76,75%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>86,35%</t>
+          <t>86,39%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>219491</t>
+          <t>219712</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>243608</t>
+          <t>244418</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>78,91%</t>
+          <t>78,99%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>87,58%</t>
+          <t>87,87%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>436200</t>
+          <t>436210</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>470742</t>
+          <t>470036</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>85,75%</t>
+          <t>85,62%</t>
         </is>
       </c>
     </row>
@@ -2560,12 +2560,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>36963</t>
+          <t>36852</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>62810</t>
+          <t>62974</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2575,12 +2575,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>34536</t>
+          <t>33726</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>58653</t>
+          <t>58432</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>78213</t>
+          <t>78919</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>112755</t>
+          <t>112745</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,7 +2645,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>479827</t>
+          <t>478686</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>519554</t>
+          <t>518008</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>78,02%</t>
+          <t>77,83%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>84,48%</t>
+          <t>84,23%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>527551</t>
+          <t>527192</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>561693</t>
+          <t>562061</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>82,79%</t>
+          <t>82,73%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>88,14%</t>
+          <t>88,2%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1020631</t>
+          <t>1020814</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1071446</t>
+          <t>1069135</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>81,5%</t>
+          <t>81,52%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>85,56%</t>
+          <t>85,38%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>95473</t>
+          <t>97019</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>135200</t>
+          <t>136341</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>75550</t>
+          <t>75182</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>109692</t>
+          <t>110051</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>180824</t>
+          <t>183135</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>231639</t>
+          <t>231456</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,48%</t>
         </is>
       </c>
     </row>
@@ -3133,12 +3133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>510364</t>
+          <t>511107</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>558071</t>
+          <t>560180</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3148,12 +3148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>68,7%</t>
+          <t>68,8%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>75,12%</t>
+          <t>75,4%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>592483</t>
+          <t>592139</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>641107</t>
+          <t>637909</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3183,12 +3183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>75,72%</t>
+          <t>75,68%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>81,94%</t>
+          <t>81,53%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1117657</t>
+          <t>1117026</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1188717</t>
+          <t>1186200</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>73,27%</t>
+          <t>73,23%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>77,93%</t>
+          <t>77,77%</t>
         </is>
       </c>
     </row>
@@ -3246,12 +3246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>184842</t>
+          <t>182733</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>232549</t>
+          <t>231806</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3261,12 +3261,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>31,2%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>141344</t>
+          <t>144542</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>189968</t>
+          <t>190312</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3296,12 +3296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>336647</t>
+          <t>339164</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>407707</t>
+          <t>408338</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3331,12 +3331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>26,77%</t>
         </is>
       </c>
     </row>
@@ -3476,12 +3476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2451498</t>
+          <t>2446669</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2550722</t>
+          <t>2543041</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3491,12 +3491,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>74,89%</t>
+          <t>74,74%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>77,92%</t>
+          <t>77,68%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2713392</t>
+          <t>2712791</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2798214</t>
+          <t>2798060</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3526,12 +3526,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>80,35%</t>
+          <t>80,33%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>82,86%</t>
+          <t>82,85%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>5185270</t>
+          <t>5188156</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5322071</t>
+          <t>5314879</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3561,12 +3561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>77,96%</t>
+          <t>78,01%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>80,02%</t>
+          <t>79,91%</t>
         </is>
       </c>
     </row>
@@ -3589,12 +3589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>722949</t>
+          <t>730630</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>822173</t>
+          <t>827002</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>578948</t>
+          <t>579102</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>663770</t>
+          <t>664371</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3639,12 +3639,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1328762</t>
+          <t>1335954</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1465563</t>
+          <t>1462677</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3674,12 +3674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>21,99%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>205169</t>
+          <t>204656</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>235257</t>
+          <t>234715</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>69,61%</t>
+          <t>69,44%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>79,82%</t>
+          <t>79,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>205206</t>
+          <t>204451</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>234980</t>
+          <t>234876</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>72,0%</t>
+          <t>71,74%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>82,45%</t>
+          <t>82,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>418631</t>
+          <t>417832</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>461671</t>
+          <t>461819</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>72,21%</t>
+          <t>72,07%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>79,63%</t>
+          <t>79,66%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>59481</t>
+          <t>60023</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>89569</t>
+          <t>90082</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,39%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>50026</t>
+          <t>50130</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>79800</t>
+          <t>80555</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>28,26%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>118073</t>
+          <t>117925</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>161113</t>
+          <t>161912</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>27,93%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>412290</t>
+          <t>413926</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>445741</t>
+          <t>446235</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>81,72%</t>
+          <t>82,05%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>88,45%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>443440</t>
+          <t>443889</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>475182</t>
+          <t>474652</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>84,66%</t>
+          <t>84,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>90,62%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>868480</t>
+          <t>866476</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>911773</t>
+          <t>911591</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>84,46%</t>
+          <t>84,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>88,65%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>58746</t>
+          <t>58252</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>92197</t>
+          <t>90561</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>48583</t>
+          <t>49113</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>80325</t>
+          <t>79876</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>116479</t>
+          <t>116661</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>159772</t>
+          <t>161776</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,73%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>273402</t>
+          <t>272833</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>295564</t>
+          <t>295687</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>84,37%</t>
+          <t>84,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>91,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>304802</t>
+          <t>305293</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>325266</t>
+          <t>325111</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>89,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>583992</t>
+          <t>585600</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>615712</t>
+          <t>615857</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>87,94%</t>
+          <t>88,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>92,74%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>28482</t>
+          <t>28359</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>50644</t>
+          <t>51213</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>14768</t>
+          <t>14923</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>35232</t>
+          <t>34741</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>48368</t>
+          <t>48223</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>80088</t>
+          <t>78480</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>11,82%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>291436</t>
+          <t>289714</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>321666</t>
+          <t>321670</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>77,93%</t>
+          <t>77,47%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>349533</t>
+          <t>349531</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>370253</t>
+          <t>369420</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>89,87%</t>
+          <t>89,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>647118</t>
+          <t>646021</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>685244</t>
+          <t>685227</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>84,82%</t>
+          <t>84,68%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>89,82%</t>
+          <t>89,81%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>52316</t>
+          <t>52312</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>82546</t>
+          <t>84268</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5217,7 +5217,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>18698</t>
+          <t>19531</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>39418</t>
+          <t>39420</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>77689</t>
+          <t>77706</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>115815</t>
+          <t>116912</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,32%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>142629</t>
+          <t>143762</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>170629</t>
+          <t>170077</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>67,08%</t>
+          <t>67,62%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>80,25%</t>
+          <t>79,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>179947</t>
+          <t>179677</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>199819</t>
+          <t>199407</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>81,95%</t>
+          <t>81,82%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>90,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>331061</t>
+          <t>329703</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>364397</t>
+          <t>365063</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>76,6%</t>
+          <t>76,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>84,46%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>41989</t>
+          <t>42541</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>69989</t>
+          <t>68856</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>32,38%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>19772</t>
+          <t>20184</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>39644</t>
+          <t>39914</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>67812</t>
+          <t>67146</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>101148</t>
+          <t>102506</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>23,72%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>232466</t>
+          <t>232864</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>252338</t>
+          <t>253029</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>85,15%</t>
+          <t>85,29%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>236628</t>
+          <t>237176</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>257961</t>
+          <t>259104</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>85,03%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>475743</t>
+          <t>475684</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>505939</t>
+          <t>506021</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>86,19%</t>
+          <t>86,18%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>91,68%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>20684</t>
+          <t>19993</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>40556</t>
+          <t>40158</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>20983</t>
+          <t>19840</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>42316</t>
+          <t>41768</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>46027</t>
+          <t>45945</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>76223</t>
+          <t>76282</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,82%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>541420</t>
+          <t>541989</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>579045</t>
+          <t>580173</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>82,07%</t>
+          <t>82,15%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>87,77%</t>
+          <t>87,94%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>585253</t>
+          <t>587143</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>622720</t>
+          <t>624142</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>84,72%</t>
+          <t>84,99%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>90,14%</t>
+          <t>90,35%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1143134</t>
+          <t>1139438</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1192712</t>
+          <t>1192001</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>84,64%</t>
+          <t>84,37%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>88,26%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>80680</t>
+          <t>79552</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>118305</t>
+          <t>117736</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>68108</t>
+          <t>66686</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>105575</t>
+          <t>103685</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>157841</t>
+          <t>158552</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>207419</t>
+          <t>211115</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,63%</t>
         </is>
       </c>
     </row>
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>625819</t>
+          <t>621966</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>667888</t>
+          <t>668481</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>80,33%</t>
+          <t>79,83%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>85,73%</t>
+          <t>85,8%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>689342</t>
+          <t>690263</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>731596</t>
+          <t>732177</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>83,67%</t>
+          <t>83,78%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>88,87%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6526,12 +6526,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1327345</t>
+          <t>1329185</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1385826</t>
+          <t>1385787</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6541,7 +6541,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>82,81%</t>
+          <t>82,92%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>111210</t>
+          <t>110617</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>153279</t>
+          <t>157132</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>92257</t>
+          <t>91676</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>134511</t>
+          <t>133590</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>217125</t>
+          <t>217164</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>275606</t>
+          <t>273766</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6659,7 +6659,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>17,08%</t>
         </is>
       </c>
     </row>
@@ -6799,12 +6799,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2801621</t>
+          <t>2807106</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2893006</t>
+          <t>2901259</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>81,88%</t>
+          <t>82,04%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>84,55%</t>
+          <t>84,79%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3070752</t>
+          <t>3078052</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3152914</t>
+          <t>3157898</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>86,68%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>88,79%</t>
+          <t>88,93%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6869,12 +6869,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>5907117</t>
+          <t>5907769</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>6026951</t>
+          <t>6028474</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6884,12 +6884,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>84,72%</t>
+          <t>84,73%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>86,44%</t>
+          <t>86,46%</t>
         </is>
       </c>
     </row>
@@ -6912,12 +6912,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>528711</t>
+          <t>520458</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>620096</t>
+          <t>614611</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>398058</t>
+          <t>393074</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>480220</t>
+          <t>472920</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>945738</t>
+          <t>944215</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1065572</t>
+          <t>1064920</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6997,12 +6997,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,27%</t>
         </is>
       </c>
     </row>
@@ -7378,12 +7378,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>207074</t>
+          <t>205482</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>236237</t>
+          <t>236424</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7393,12 +7393,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>70,98%</t>
+          <t>70,44%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>80,98%</t>
+          <t>81,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>219286</t>
+          <t>218761</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>246345</t>
+          <t>246292</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7428,12 +7428,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>75,96%</t>
+          <t>75,77%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>85,33%</t>
+          <t>85,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7448,12 +7448,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>435131</t>
+          <t>433840</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>475753</t>
+          <t>475872</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7463,12 +7463,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>74,97%</t>
+          <t>74,74%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>81,97%</t>
+          <t>81,99%</t>
         </is>
       </c>
     </row>
@@ -7491,12 +7491,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>55491</t>
+          <t>55304</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>84654</t>
+          <t>86246</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7506,12 +7506,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>42358</t>
+          <t>42411</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>69417</t>
+          <t>69942</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7541,12 +7541,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7561,12 +7561,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>104678</t>
+          <t>104559</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>145300</t>
+          <t>146591</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7576,12 +7576,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>25,26%</t>
         </is>
       </c>
     </row>
@@ -7721,12 +7721,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>414254</t>
+          <t>412952</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>445803</t>
+          <t>446072</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7736,12 +7736,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>82,43%</t>
+          <t>82,17%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>88,7%</t>
+          <t>88,76%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>465373</t>
+          <t>464432</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>490279</t>
+          <t>491571</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7771,12 +7771,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>88,97%</t>
+          <t>88,79%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7791,12 +7791,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>884847</t>
+          <t>888316</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>927569</t>
+          <t>930024</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7806,12 +7806,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>86,27%</t>
+          <t>86,61%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>90,68%</t>
         </is>
       </c>
     </row>
@@ -7834,12 +7834,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>56772</t>
+          <t>56503</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>88321</t>
+          <t>89623</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7849,12 +7849,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>32805</t>
+          <t>31513</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>57711</t>
+          <t>58652</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7884,12 +7884,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7904,12 +7904,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>98090</t>
+          <t>95635</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>140812</t>
+          <t>137343</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7919,12 +7919,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,39%</t>
         </is>
       </c>
     </row>
@@ -8064,12 +8064,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>252897</t>
+          <t>252694</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>278921</t>
+          <t>279095</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8079,12 +8079,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>79,39%</t>
+          <t>79,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>87,56%</t>
+          <t>87,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>277258</t>
+          <t>278227</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>302348</t>
+          <t>303129</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8114,12 +8114,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>82,44%</t>
+          <t>82,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>89,9%</t>
+          <t>90,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8134,12 +8134,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>538413</t>
+          <t>540122</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>575078</t>
+          <t>575729</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8149,12 +8149,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>82,22%</t>
+          <t>82,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>87,91%</t>
         </is>
       </c>
     </row>
@@ -8177,12 +8177,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>39644</t>
+          <t>39470</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>65668</t>
+          <t>65871</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8192,12 +8192,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>33961</t>
+          <t>33180</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>59051</t>
+          <t>58082</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8227,12 +8227,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8247,12 +8247,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>79796</t>
+          <t>79145</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>116461</t>
+          <t>114752</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8262,12 +8262,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,52%</t>
         </is>
       </c>
     </row>
@@ -8407,12 +8407,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>280302</t>
+          <t>277787</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>310991</t>
+          <t>310766</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8422,12 +8422,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>75,76%</t>
+          <t>75,08%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>84,06%</t>
+          <t>84,0%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8442,12 +8442,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>316517</t>
+          <t>318121</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>345591</t>
+          <t>346289</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8457,12 +8457,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>81,73%</t>
+          <t>82,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>89,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8477,12 +8477,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>607221</t>
+          <t>606638</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>649629</t>
+          <t>648190</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8492,12 +8492,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>80,19%</t>
+          <t>80,11%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>85,79%</t>
+          <t>85,6%</t>
         </is>
       </c>
     </row>
@@ -8520,12 +8520,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>58973</t>
+          <t>59198</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>89662</t>
+          <t>92177</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8535,12 +8535,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8555,12 +8555,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>41692</t>
+          <t>40994</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>70766</t>
+          <t>69162</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8570,12 +8570,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>107618</t>
+          <t>109057</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>150026</t>
+          <t>150609</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8605,12 +8605,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>19,89%</t>
         </is>
       </c>
     </row>
@@ -8750,12 +8750,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>182397</t>
+          <t>184036</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>199804</t>
+          <t>199744</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8765,12 +8765,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>86,35%</t>
+          <t>87,13%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8785,12 +8785,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>197872</t>
+          <t>197698</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>211449</t>
+          <t>211467</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8800,12 +8800,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>90,44%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8820,12 +8820,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>386374</t>
+          <t>386555</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>408689</t>
+          <t>407692</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8835,12 +8835,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>94,85%</t>
         </is>
       </c>
     </row>
@@ -8863,12 +8863,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11417</t>
+          <t>11477</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>28824</t>
+          <t>27185</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8878,12 +8878,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8898,12 +8898,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7138</t>
+          <t>7120</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>20715</t>
+          <t>20889</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8913,12 +8913,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8933,12 +8933,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>21119</t>
+          <t>22116</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>43434</t>
+          <t>43253</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8948,12 +8948,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,06%</t>
         </is>
       </c>
     </row>
@@ -9093,12 +9093,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>146049</t>
+          <t>145654</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>178656</t>
+          <t>177255</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>55,51%</t>
+          <t>55,36%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>67,9%</t>
+          <t>67,37%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9128,12 +9128,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>159833</t>
+          <t>159545</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>193494</t>
+          <t>192843</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9143,12 +9143,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>58,74%</t>
+          <t>58,63%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>71,11%</t>
+          <t>70,87%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>315333</t>
+          <t>315826</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>361406</t>
+          <t>362821</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9178,12 +9178,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>58,92%</t>
+          <t>59,01%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>67,52%</t>
+          <t>67,79%</t>
         </is>
       </c>
     </row>
@@ -9206,12 +9206,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>84467</t>
+          <t>85868</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>117074</t>
+          <t>117469</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>32,63%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>44,49%</t>
+          <t>44,64%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9241,12 +9241,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>78609</t>
+          <t>79260</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>112270</t>
+          <t>112558</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9256,12 +9256,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>41,37%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9276,12 +9276,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>173820</t>
+          <t>172405</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>219893</t>
+          <t>219400</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9291,12 +9291,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>32,21%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>41,08%</t>
+          <t>40,99%</t>
         </is>
       </c>
     </row>
@@ -9436,12 +9436,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>445934</t>
+          <t>445220</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>494493</t>
+          <t>494722</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9451,12 +9451,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>68,31%</t>
+          <t>68,2%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>75,75%</t>
+          <t>75,79%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9471,12 +9471,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>496867</t>
+          <t>497501</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>544324</t>
+          <t>542781</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9486,12 +9486,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>71,99%</t>
+          <t>72,08%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>78,87%</t>
+          <t>78,64%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9506,12 +9506,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>955082</t>
+          <t>955215</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1023547</t>
+          <t>1025119</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9521,12 +9521,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>71,12%</t>
+          <t>71,13%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>76,22%</t>
+          <t>76,33%</t>
         </is>
       </c>
     </row>
@@ -9549,12 +9549,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>158285</t>
+          <t>158056</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>206844</t>
+          <t>207558</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>31,8%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9584,12 +9584,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>145858</t>
+          <t>147401</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>193315</t>
+          <t>192681</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9599,12 +9599,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9619,12 +9619,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>319412</t>
+          <t>317840</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>387877</t>
+          <t>387744</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9634,12 +9634,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>28,88%</t>
+          <t>28,87%</t>
         </is>
       </c>
     </row>
@@ -9779,12 +9779,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>650847</t>
+          <t>650291</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>691149</t>
+          <t>689369</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9794,12 +9794,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>83,7%</t>
+          <t>83,63%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>88,65%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9814,12 +9814,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>687708</t>
+          <t>688111</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>729299</t>
+          <t>729410</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9829,12 +9829,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>83,62%</t>
+          <t>83,66%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>88,69%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9849,12 +9849,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1352658</t>
+          <t>1352594</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1406901</t>
+          <t>1406781</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9864,12 +9864,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>84,54%</t>
+          <t>84,53%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>87,92%</t>
         </is>
       </c>
     </row>
@@ -9892,12 +9892,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>86447</t>
+          <t>88227</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>126749</t>
+          <t>127305</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9907,12 +9907,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9927,12 +9927,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>93163</t>
+          <t>93052</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>134754</t>
+          <t>134351</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9942,12 +9942,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9962,12 +9962,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>193157</t>
+          <t>193277</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>247400</t>
+          <t>247464</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9977,12 +9977,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,47%</t>
         </is>
       </c>
     </row>
@@ -10122,12 +10122,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2663191</t>
+          <t>2663723</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2759808</t>
+          <t>2756120</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10137,12 +10137,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>78,62%</t>
+          <t>78,63%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>81,47%</t>
+          <t>81,36%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10157,12 +10157,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2906414</t>
+          <t>2902820</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2999309</t>
+          <t>2994356</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10172,12 +10172,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>82,13%</t>
+          <t>82,03%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>84,76%</t>
+          <t>84,62%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10192,12 +10192,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>5597182</t>
+          <t>5591746</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5726172</t>
+          <t>5728970</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10207,12 +10207,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>80,81%</t>
+          <t>80,73%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>82,67%</t>
+          <t>82,71%</t>
         </is>
       </c>
     </row>
@@ -10235,12 +10235,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>627742</t>
+          <t>631430</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>724359</t>
+          <t>723827</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10250,12 +10250,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10270,12 +10270,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>539403</t>
+          <t>544356</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>632298</t>
+          <t>635892</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10285,12 +10285,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10305,12 +10305,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1200091</t>
+          <t>1197293</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1329081</t>
+          <t>1334517</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10320,12 +10320,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>19,27%</t>
         </is>
       </c>
     </row>
